--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -1422,16 +1422,12 @@
       <c r="H3" s="10" t="n">
         <v>0.026</v>
       </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX (CLUSTER=CLID)</t>
-        </is>
-      </c>
+      <c r="I3" s="10" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1" s="16">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Empowering leadership (parcels)</t>
+          <t>Empowering leadership</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
@@ -1455,11 +1451,7 @@
       <c r="H4" s="10" t="n">
         <v>0.014</v>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I4" s="10" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="16">
       <c r="A5" s="10" t="inlineStr">
@@ -1488,11 +1480,7 @@
       <c r="H5" s="10" t="n">
         <v>0.038</v>
       </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I5" s="10" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="16">
       <c r="A6" s="10" t="inlineStr">
@@ -1521,11 +1509,7 @@
       <c r="H6" s="10" t="n">
         <v>0.032</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I6" s="10" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="16">
       <c r="A7" s="10" t="inlineStr">
@@ -1554,11 +1538,7 @@
       <c r="H7" s="10" t="n">
         <v>0.021</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I7" s="10" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="16">
       <c r="A8" s="10" t="inlineStr">
@@ -1587,16 +1567,12 @@
       <c r="H8" s="10" t="n">
         <v>0.034</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I8" s="10" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1" s="16">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Thriving (parcels)</t>
+          <t>Thriving</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
@@ -1622,7 +1598,7 @@
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>Items 5 and 10 reverse-coded; MLR / TYPE=COMPLEX</t>
+          <t>Items 5 and 10 reverse-coded</t>
         </is>
       </c>
     </row>
@@ -1653,11 +1629,7 @@
       <c r="H10" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I10" s="10" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="16">
       <c r="A11" s="10" t="inlineStr">
@@ -1686,11 +1658,7 @@
       <c r="H11" s="10" t="n">
         <v>0.029</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I11" s="10" t="n"/>
     </row>
     <row r="14" ht="20.25" customFormat="1" customHeight="1" s="13">
       <c r="A14" s="8" t="inlineStr">
@@ -1773,11 +1741,7 @@
       <c r="H16" s="10" t="n">
         <v>0.025</v>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I16" s="10" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1" s="16">
       <c r="A17" s="10" t="inlineStr">
@@ -1806,11 +1770,7 @@
       <c r="H17" s="10" t="n">
         <v>0.018</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>MLR / TYPE=COMPLEX</t>
-        </is>
-      </c>
+      <c r="I17" s="10" t="n"/>
     </row>
     <row r="21" ht="22.5" customHeight="1" s="16">
       <c r="A21" s="15" t="n"/>
@@ -1892,7 +1852,7 @@
     <row r="4" ht="45" customHeight="1" s="16">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Two-factor: self-rated OCBS / CWBS</t>
+          <t>Two-factor model: self-rated OCBS and self-rated CWBS</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
@@ -1913,16 +1873,12 @@
       <c r="G4" s="10" t="n">
         <v>0.034</v>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>Retained</t>
-        </is>
-      </c>
+      <c r="H4" s="10" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1" s="16">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>One-factor: self-rated OCBS+CWBS</t>
+          <t>One-factor model: self-rated OCBS and self-rated CWBS combined</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
@@ -1943,16 +1899,12 @@
       <c r="G5" s="10" t="n">
         <v>0.094</v>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1" s="16">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Two-factor: leader-rated OCBS / CWBS</t>
+          <t>Two-factor model: leader-rated OCBS and leader-rated CWBS</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
@@ -1973,16 +1925,12 @@
       <c r="G6" s="10" t="n">
         <v>0.031</v>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Retained</t>
-        </is>
-      </c>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1" s="16">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>One-factor: leader-rated OCBS+CWBS</t>
+          <t>One-factor model: leader-rated OCBS and leader-rated CWBS combined</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
@@ -2003,11 +1951,7 @@
       <c r="G7" s="10" t="n">
         <v>0.097</v>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
+      <c r="H7" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>2.18</v>
+        <v>81</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.998</v>
+        <v>0.962</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.995</v>
+        <v>0.954</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>0.014</v>
+        <v>0.038</v>
       </c>
       <c r="I4" s="10" t="n"/>
     </row>
@@ -1576,25 +1576,25 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>3.12</v>
+        <v>57.75</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.994</v>
+        <v>0.952</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.982</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.022</v>
+        <v>0.04</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>42.3</v>
+        <v>53.4</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.977</v>
+        <v>0.976</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.965</v>
+        <v>0.969</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.038</v>
+        <v>0.026</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.034</v>
+        <v>0.028</v>
       </c>
       <c r="H4" s="10" t="n"/>
     </row>
@@ -1882,22 +1882,22 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>134.7</v>
+        <v>138.6</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.802</v>
+        <v>0.792</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.762</v>
+        <v>0.74</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.117</v>
+        <v>0.11</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.094</v>
+        <v>0.095</v>
       </c>
       <c r="H5" s="10" t="n"/>
     </row>
@@ -1908,22 +1908,22 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>39.8</v>
+        <v>49.5</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.984</v>
+        <v>0.985</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.974</v>
+        <v>0.981</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.034</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.031</v>
+        <v>0.025</v>
       </c>
       <c r="H6" s="10" t="n"/>
     </row>
@@ -1934,22 +1934,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>142.6</v>
+        <v>141.9</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.751</v>
+        <v>0.733</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.122</v>
+        <v>0.114</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="H7" s="10" t="n"/>
     </row>

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -2194,12 +2194,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>-0.078 (0.038)</t>
+          <t>0.078 (0.038)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>-0.081 (0.038)</t>
+          <t>0.081 (0.038)</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>0.098 (0.039)</t>
+          <t>-0.098 (0.039)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>0.103 (0.039)</t>
+          <t>-0.103 (0.039)</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>0.111 (0.041)</t>
+          <t>-0.111 (0.041)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>0.116 (0.041)</t>
+          <t>-0.116 (0.041)</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>-0.067 (0.038)</t>
+          <t>0.067 (0.038)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>-0.071 (0.038)</t>
+          <t>0.071 (0.038)</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>-0.078 (0.038)</t>
+          <t>0.078 (0.038)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>-0.075 (0.040)</t>
+          <t>0.075 (0.040)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>0.098 (0.039)</t>
+          <t>-0.098 (0.039)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>0.094 (0.041)</t>
+          <t>-0.094 (0.041)</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>0.111 (0.041)</t>
+          <t>-0.111 (0.041)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>0.107 (0.043)</t>
+          <t>-0.107 (0.043)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>-0.067 (0.038)</t>
+          <t>0.067 (0.038)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>-0.064 (0.040)</t>
+          <t>0.064 (0.040)</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -2199,7 +2199,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>0.081 (0.038)</t>
+          <t>0.078 (0.038)</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>-0.103 (0.039)</t>
+          <t>-0.098 (0.039)</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>-0.014 (0.040)</t>
+          <t>-0.012 (0.040)</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>0.019 (0.039)</t>
+          <t>0.018 (0.039)</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>-0.116 (0.041)</t>
+          <t>-0.111 (0.041)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>0.071 (0.038)</t>
+          <t>0.067 (0.038)</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>0.026 (0.043)</t>
+          <t>0.024 (0.043)</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>-0.021 (0.041)</t>
+          <t>-0.019 (0.041)</t>
         </is>
       </c>
     </row>

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>0.203 (0.048)</t>
+          <t>0.284 (0.052)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>0.219 (0.046)</t>
+          <t>0.318 (0.052)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>-0.112 (0.044)</t>
+          <t>-0.212 (0.046)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>-0.124 (0.043)</t>
+          <t>-0.065 (0.049)</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>-0.156 (0.053)</t>
+          <t>-0.170 (0.055)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>-0.171 (0.051)</t>
+          <t>-0.153 (0.054)</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>0.278 (0.055)</t>
+          <t>0.184 (0.049)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0.292 (0.054)</t>
+          <t>0.344 (0.052)</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>-0.142 (0.052)</t>
+          <t>-0.496 (0.064)</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>-0.142 (0.052)</t>
+          <t>-0.496 (0.064)</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>0.267 (0.049)</t>
+          <t>0.523 (0.059)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>0.267 (0.049)</t>
+          <t>0.523 (0.059)</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>0.312 (0.058)</t>
+          <t>0.571 (0.061)</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>0.312 (0.058)</t>
+          <t>0.571 (0.061)</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>-0.145 (0.052)</t>
+          <t>-0.402 (0.057)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>-0.145 (0.052)</t>
+          <t>-0.402 (0.057)</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>0.078 (0.038)</t>
+          <t>-0.023 (0.067)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>0.078 (0.038)</t>
+          <t>-0.023 (0.067)</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>-0.098 (0.039)</t>
+          <t>-0.153 (0.063)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>-0.098 (0.039)</t>
+          <t>-0.153 (0.063)</t>
         </is>
       </c>
     </row>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>-0.012 (0.040)</t>
+          <t>-0.042 (0.075)</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>-0.012 (0.040)</t>
+          <t>-0.042 (0.075)</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>-0.142 (0.052)</t>
+          <t>-0.496 (0.064)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>-0.137 (0.054)</t>
+          <t>-0.481 (0.066)</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>0.267 (0.049)</t>
+          <t>0.523 (0.059)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>0.258 (0.051)</t>
+          <t>0.508 (0.061)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>0.312 (0.058)</t>
+          <t>0.571 (0.061)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>0.302 (0.060)</t>
+          <t>0.554 (0.063)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>-0.145 (0.052)</t>
+          <t>-0.402 (0.057)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.139 (0.054)</t>
+          <t>-0.390 (0.058)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0.234 (0.046)</t>
+          <t>0.199 (0.034)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0.228 (0.048)</t>
+          <t>0.193 (0.035)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.203 (0.048)</t>
+          <t>0.284 (0.052)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>0.197 (0.050)</t>
+          <t>0.276 (0.054)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-0.112 (0.044)</t>
+          <t>-0.212 (0.046)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>-0.108 (0.046)</t>
+          <t>-0.206 (0.048)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>-0.198 (0.051)</t>
+          <t>-0.137 (0.035)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>-0.192 (0.053)</t>
+          <t>-0.133 (0.036)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>-0.156 (0.053)</t>
+          <t>-0.170 (0.055)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>-0.151 (0.055)</t>
+          <t>-0.165 (0.057)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>0.278 (0.055)</t>
+          <t>0.184 (0.049)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0.270 (0.057)</t>
+          <t>0.178 (0.050)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>0.078 (0.038)</t>
+          <t>-0.023 (0.067)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>0.075 (0.040)</t>
+          <t>-0.023 (0.069)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>0.284 (0.052)</t>
+          <t>0.319 (0.057)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>0.318 (0.052)</t>
+          <t>0.451 (0.056)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>-0.212 (0.046)</t>
+          <t>-0.282 (0.052)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>-0.065 (0.049)</t>
+          <t>-0.230 (0.055)</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>-0.170 (0.055)</t>
+          <t>-0.257 (0.064)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>-0.153 (0.054)</t>
+          <t>-0.409 (0.061)</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>0.184 (0.049)</t>
+          <t>0.268 (0.057)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0.344 (0.052)</t>
+          <t>0.467 (0.060)</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>0.571 (0.061)</t>
+          <t>0.588 (0.058)</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>0.571 (0.061)</t>
+          <t>0.588 (0.058)</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>-0.402 (0.057)</t>
+          <t>-0.385 (0.054)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>-0.402 (0.057)</t>
+          <t>-0.385 (0.054)</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>0.571 (0.061)</t>
+          <t>0.588 (0.058)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>0.554 (0.063)</t>
+          <t>0.570 (0.060)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>-0.402 (0.057)</t>
+          <t>-0.385 (0.054)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.390 (0.058)</t>
+          <t>-0.374 (0.056)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0.199 (0.034)</t>
+          <t>0.249 (0.037)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0.193 (0.035)</t>
+          <t>0.241 (0.039)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.284 (0.052)</t>
+          <t>0.319 (0.057)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>0.276 (0.054)</t>
+          <t>0.309 (0.059)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-0.212 (0.046)</t>
+          <t>-0.282 (0.052)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>-0.206 (0.048)</t>
+          <t>-0.273 (0.053)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>-0.137 (0.035)</t>
+          <t>-0.222 (0.041)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>-0.133 (0.036)</t>
+          <t>-0.215 (0.042)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>-0.170 (0.055)</t>
+          <t>-0.257 (0.064)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>-0.165 (0.057)</t>
+          <t>-0.250 (0.066)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>0.184 (0.049)</t>
+          <t>0.268 (0.057)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0.178 (0.050)</t>
+          <t>0.260 (0.059)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>0.319 (0.057)</t>
+          <t>0.300 (0.057)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>0.451 (0.056)</t>
+          <t>0.423 (0.058)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>-0.282 (0.052)</t>
+          <t>-0.264 (0.051)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>-0.230 (0.055)</t>
+          <t>-0.205 (0.057)</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>-0.257 (0.064)</t>
+          <t>-0.252 (0.065)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>-0.409 (0.061)</t>
+          <t>-0.417 (0.066)</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>0.268 (0.057)</t>
+          <t>0.262 (0.058)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0.467 (0.060)</t>
+          <t>0.484 (0.066)</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0.249 (0.037)</t>
+          <t>0.239 (0.036)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0.241 (0.039)</t>
+          <t>0.232 (0.037)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.319 (0.057)</t>
+          <t>0.300 (0.057)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>0.309 (0.059)</t>
+          <t>0.291 (0.059)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-0.282 (0.052)</t>
+          <t>-0.264 (0.051)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>-0.273 (0.053)</t>
+          <t>-0.256 (0.053)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>-0.222 (0.041)</t>
+          <t>-0.219 (0.042)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>-0.215 (0.042)</t>
+          <t>-0.213 (0.044)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>-0.257 (0.064)</t>
+          <t>-0.252 (0.065)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>-0.250 (0.066)</t>
+          <t>-0.244 (0.067)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>0.268 (0.057)</t>
+          <t>0.262 (0.058)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0.260 (0.059)</t>
+          <t>0.254 (0.060)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">

--- a/results/study3附录结果填答.xlsx
+++ b/results/study3附录结果填答.xlsx
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>0.300 (0.057)</t>
+          <t>0.053 (0.064)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>0.423 (0.058)</t>
+          <t>0.422 (0.058)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>-0.264 (0.051)</t>
+          <t>-0.280 (0.053)</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>-0.205 (0.057)</t>
+          <t>-0.211 (0.057)</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>-0.252 (0.065)</t>
+          <t>-0.034 (0.075)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>-0.417 (0.066)</t>
+          <t>-0.396 (0.066)</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>0.262 (0.058)</t>
+          <t>0.040 (0.061)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>0.484 (0.066)</t>
+          <t>0.456 (0.066)</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0.239 (0.036)</t>
+          <t>0.090 (0.044)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0.232 (0.037)</t>
+          <t>0.087 (0.046)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.300 (0.057)</t>
+          <t>0.053 (0.064)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>0.291 (0.059)</t>
+          <t>0.052 (0.066)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-0.264 (0.051)</t>
+          <t>-0.280 (0.053)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>-0.256 (0.053)</t>
+          <t>-0.272 (0.054)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>-0.219 (0.042)</t>
+          <t>-0.122 (0.054)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>-0.213 (0.044)</t>
+          <t>-0.119 (0.056)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>-0.252 (0.065)</t>
+          <t>-0.034 (0.075)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>-0.244 (0.067)</t>
+          <t>-0.033 (0.077)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>0.262 (0.058)</t>
+          <t>0.040 (0.061)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0.254 (0.060)</t>
+          <t>0.039 (0.063)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
